--- a/docs/templates/hotel-contract-import-template.xlsx
+++ b/docs/templates/hotel-contract-import-template.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\dmc-platform\docs\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12ED5052-0B99-457A-85DC-D2997EE37B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="2940" yWindow="1980" windowWidth="14400" windowHeight="7280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Meta" sheetId="1" r:id="rId1"/>
     <sheet name="Rates" sheetId="2" r:id="rId2"/>
@@ -11,37 +21,237 @@
     <sheet name="CancellationPolicy" sheetId="6" r:id="rId6"/>
     <sheet name="RatePolicies" sheetId="7" r:id="rId7"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="73">
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Hotel Name</t>
+  </si>
+  <si>
+    <t>Grand Petra Hotel</t>
+  </si>
+  <si>
+    <t>Supplier Name</t>
+  </si>
+  <si>
+    <t>Contract Name</t>
+  </si>
+  <si>
+    <t>Grand Petra Hotel 2026</t>
+  </si>
+  <si>
+    <t>Valid From</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>Valid To</t>
+  </si>
+  <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>JOD</t>
+  </si>
+  <si>
+    <t>Default Tax Percent</t>
+  </si>
+  <si>
+    <t>Tax Included</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Default Service Percent</t>
+  </si>
+  <si>
+    <t>Service Included</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Amman</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>5 Star</t>
+  </si>
+  <si>
+    <t>Room Type</t>
+  </si>
+  <si>
+    <t>Occupancy</t>
+  </si>
+  <si>
+    <t>Meal Plan</t>
+  </si>
+  <si>
+    <t>Season From</t>
+  </si>
+  <si>
+    <t>Season To</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Pricing Basis</t>
+  </si>
+  <si>
+    <t>Tax %</t>
+  </si>
+  <si>
+    <t>Service %</t>
+  </si>
+  <si>
+    <t>Deluxe Room</t>
+  </si>
+  <si>
+    <t>DBL</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>PER_ROOM</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>DLX</t>
+  </si>
+  <si>
+    <t>Deluxe room imported from the contract template.</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Charge Basis</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Mandatory</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Extra Bed</t>
+  </si>
+  <si>
+    <t>EXTRA_BED</t>
+  </si>
+  <si>
+    <t>PER_NIGHT</t>
+  </si>
+  <si>
+    <t>Optional extra bed per night.</t>
+  </si>
+  <si>
+    <t>Child Policy</t>
+  </si>
+  <si>
+    <t>Children below 6 stay free when sharing existing bedding.</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>No Show Penalty Type</t>
+  </si>
+  <si>
+    <t>No Show Penalty Value</t>
+  </si>
+  <si>
+    <t>Days Before</t>
+  </si>
+  <si>
+    <t>Window To</t>
+  </si>
+  <si>
+    <t>Deadline Unit</t>
+  </si>
+  <si>
+    <t>Penalty Type</t>
+  </si>
+  <si>
+    <t>Penalty Value</t>
+  </si>
+  <si>
+    <t>Cancellation policy imported from Excel template.</t>
+  </si>
+  <si>
+    <t>FULL_STAY</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>DAYS</t>
+  </si>
+  <si>
+    <t>PERCENT</t>
+  </si>
+  <si>
+    <t>50% penalty within 14 days before arrival.</t>
+  </si>
+  <si>
+    <t>Policy Type</t>
+  </si>
+  <si>
+    <t>Applies To</t>
+  </si>
+  <si>
+    <t>Age From</t>
+  </si>
+  <si>
+    <t>Age To</t>
+  </si>
+  <si>
+    <t>Percent</t>
+  </si>
+  <si>
+    <t>CHILD_FREE</t>
+  </si>
+  <si>
+    <t>Child sharing existing bedding</t>
+  </si>
+  <si>
+    <t>Child free policy for children 0-5.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -71,13 +281,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -402,420 +620,413 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="1" max="2" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Key</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Hotel Name</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Grand Petra Hotel</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Supplier Name</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Grand Petra Hotel</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Contract Name</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Grand Petra Hotel 2026</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Valid From</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-01-01</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Valid To</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-12-31</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Currency</v>
-      </c>
-      <c r="B7" t="str">
-        <v>JOD</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Default Tax Percent</v>
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
       </c>
       <c r="B8">
         <v>8</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Tax Included</v>
-      </c>
-      <c r="B9" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Default Service Percent</v>
+    <row r="9" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>16</v>
       </c>
       <c r="B10">
         <v>5</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Service Included</v>
-      </c>
-      <c r="B11" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>City</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Amman</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Category</v>
-      </c>
-      <c r="B13" t="str">
-        <v>5 Star</v>
+    <row r="11" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
+    <ignoredError sqref="A1:B13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="1" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="9" max="11" width="14.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Room Type</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Occupancy</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Meal Plan</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Season From</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Season To</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Cost</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Currency</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Pricing Basis</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Tax %</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Tax Included</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Service %</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Service Included</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Deluxe Room</v>
-      </c>
-      <c r="B2" t="str">
-        <v>DBL</v>
-      </c>
-      <c r="C2" t="str">
-        <v>BB</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2026-12-31</v>
+    <row r="1" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
       </c>
       <c r="F2">
         <v>120</v>
       </c>
-      <c r="G2" t="str">
-        <v>JOD</v>
-      </c>
-      <c r="H2" t="str">
-        <v>PER_ROOM</v>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
       </c>
       <c r="I2">
         <v>8</v>
       </c>
-      <c r="J2" t="str">
-        <v>No</v>
+      <c r="J2" t="s">
+        <v>15</v>
       </c>
       <c r="K2">
         <v>5</v>
       </c>
-      <c r="L2" t="str">
-        <v>No</v>
+      <c r="L2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError sqref="A1:L2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="1" max="3" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Code</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Description</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Deluxe Room</v>
-      </c>
-      <c r="B2" t="str">
-        <v>DLX</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Deluxe room imported from the contract template.</v>
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError sqref="A1:C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="1" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="7" max="8" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Charge Basis</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Amount</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Currency</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Pricing Basis</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Mandatory</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Extra Bed</v>
-      </c>
-      <c r="B2" t="str">
-        <v>EXTRA_BED</v>
-      </c>
-      <c r="C2" t="str">
-        <v>PER_NIGHT</v>
+    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
       </c>
       <c r="D2">
         <v>35</v>
       </c>
-      <c r="E2" t="str">
-        <v>JOD</v>
-      </c>
-      <c r="F2" t="str">
-        <v>PER_ROOM</v>
-      </c>
-      <c r="G2" t="str">
-        <v>No</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Optional extra bed per night.</v>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError sqref="A1:H2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="1" max="2" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Child Policy</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Children below 6 stay free when sharing existing bedding.</v>
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
     <col min="3" max="3" width="23.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="4" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="15.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Summary</v>
-      </c>
-      <c r="B1" t="str">
-        <v>No Show Penalty Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>No Show Penalty Value</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Days Before</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Window To</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Deadline Unit</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Penalty Type</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Penalty Value</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Cancellation policy imported from Excel template.</v>
-      </c>
-      <c r="B2" t="str">
-        <v>FULL_STAY</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
+    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
       </c>
       <c r="D2">
         <v>14</v>
@@ -823,80 +1034,75 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" t="str">
-        <v>DAYS</v>
-      </c>
-      <c r="G2" t="str">
-        <v>PERCENT</v>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" t="s">
+        <v>63</v>
       </c>
       <c r="H2">
         <v>50</v>
       </c>
-      <c r="I2" t="str">
-        <v>50% penalty within 14 days before arrival.</v>
+      <c r="I2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError sqref="A1:I2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="1" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="9" max="10" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Policy Type</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Applies To</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Age From</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Age To</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Amount</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Percent</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Currency</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Pricing Basis</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Meal Plan</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>CHILD_FREE</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Child sharing existing bedding</v>
+    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -904,28 +1110,29 @@
       <c r="D2">
         <v>5</v>
       </c>
-      <c r="E2" t="str">
-        <v/>
+      <c r="E2" t="s">
+        <v>61</v>
       </c>
       <c r="F2">
         <v>100</v>
       </c>
-      <c r="G2" t="str">
-        <v>JOD</v>
-      </c>
-      <c r="H2" t="str">
-        <v>PER_ROOM</v>
-      </c>
-      <c r="I2" t="str">
-        <v>BB</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Child free policy for children 0-5.</v>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>